--- a/input/PL/reg_employmentSelection.xlsx
+++ b/input/PL/reg_employmentSelection.xlsx
@@ -17,24 +17,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="190" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="200" uniqueCount="45">
   <si>
-    <t>Description:</t>
-  </si>
-  <si>
-    <t>This file contains regression estimates from the first stage of the Heckman selection model used to estimates wages.</t>
+    <t>Description</t>
   </si>
   <si>
     <t>Authors:</t>
   </si>
   <si>
-    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
-  </si>
-  <si>
     <t>Last edit:</t>
   </si>
   <si>
-    <t>12 Jan 2016 AB</t>
+    <t/>
   </si>
   <si>
     <t>Process:</t>
@@ -43,25 +37,37 @@
     <t>W1fa-sel</t>
   </si>
   <si>
-    <t>First stage Heckman selection estimates for women that do not have an observed wage in the previous year</t>
-  </si>
-  <si>
     <t>W1ma-sel</t>
   </si>
   <si>
     <t>W1fb-sel</t>
   </si>
   <si>
+    <t>W1mb-sel</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Thisfilecontainsregressiones</t>
+  </si>
+  <si>
+    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
+  </si>
+  <si>
+    <t>12 Jan 2016 AB</t>
+  </si>
+  <si>
+    <t>Description:</t>
+  </si>
+  <si>
+    <t>First stage Heckman selection estimates for women that do not have an observed wage in the previous year</t>
+  </si>
+  <si>
     <t>First stage Heckman selection estimates for women that have an observed wage in the previous year</t>
   </si>
   <si>
-    <t>W1mb-sel</t>
-  </si>
-  <si>
     <t>First stage Heckman selection estimates for men that have an observed wage in the previous year</t>
-  </si>
-  <si>
-    <t>Notes:</t>
   </si>
   <si>
     <t>Estimated on panel data unlike the labour supply estimates</t>
@@ -80,9 +86,6 @@
   </si>
   <si>
     <t>REGRESSOR</t>
-  </si>
-  <si>
-    <t>COEFFICIENT</t>
   </si>
   <si>
     <t>Les_c3_Student_L1</t>
@@ -147,69 +150,18 @@
   <si>
     <t>Constant</t>
   </si>
+  <si>
+    <t>COEFFICIENT</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="13">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -220,7 +172,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -228,78 +180,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -313,95 +201,131 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>14</v>
+      <c r="A12" t="s">
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -415,1563 +339,1563 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1">
         <v>-1.6157825780773145</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0.0011982699977212141</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>0.00010021117481153152</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>4.68275445060986e-05</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>-4.691237486830668e-07</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-1.3370232582510152e-05</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>-0.0002070734575412551</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>-2.8192486626752265e-07</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>3.2746175819342787e-06</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>5.610152960977531e-05</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>-0.00028798624355746722</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>-1.71730661914179e-06</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>-1.1550476274639013e-06</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>6.8277621143589739e-06</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>-1.3458824438210889e-05</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>7.1818334577563201e-06</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>4.5567919783054414e-06</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>2.1398457000646714e-06</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>-1.9323207073742462e-06</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>6.5720317889360439e-06</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>1.2437030710985219e-06</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="1">
         <v>-0.0011787406646399177</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1">
         <v>-2.5196783554666191</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>0.00010021117481153152</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.00017571538777167792</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>6.5709954450851189e-06</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>-6.4154231320832507e-08</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>-1.4247455701788605e-05</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>-9.2744866889093169e-06</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>-4.1564544758147721e-07</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>-8.475180703836633e-07</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>-1.1452839041791173e-06</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>1.7717386314506317e-05</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>5.5729388688274025e-06</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>9.8198473013467286e-06</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>1.6944553053267536e-05</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>1.7858176055743041e-05</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>1.5673150154315448e-06</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>-8.5989562211687659e-08</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>-1.2084758536620781e-07</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>5.3632019535039189e-06</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>5.3034535509519079e-06</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>2.7105214198764388e-07</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>-0.00021467551396000859</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1">
         <v>0.1579680527012868</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>4.68275445060986e-05</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>6.5709954450851189e-06</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>1.4564466081625969e-05</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>-1.5019931834301999e-07</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>4.8681643496100329e-05</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>3.6508751168161889e-05</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>-1.1049430494541221e-06</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>-7.742283137847424e-07</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>-1.6461454327505156e-05</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>4.1890966680558335e-05</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>6.64586002047606e-07</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>3.5539699259572568e-06</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>5.090529931996824e-06</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>1.5245838117320466e-05</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>3.7839968996792708e-07</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>1.1426837785570177e-06</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>-6.8579926141857746e-07</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>4.5814455026578871e-07</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>6.3199444070117016e-07</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>5.1308609260046722e-07</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="1">
         <v>-0.00032147168797014053</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1">
         <v>-0.0020161934569374782</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>-4.691237486830668e-07</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>-6.4154231320832507e-08</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>-1.5019931834301999e-07</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>1.6501144215136645e-09</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>-1.5669957181769654e-07</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>-3.3011429192371133e-08</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>3.1310273507272825e-09</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>-3.0598656652206113e-10</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>1.7609059308883614e-07</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-4.7155516041544943e-07</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>-1.1382547707090519e-08</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-4.4724517688740138e-08</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-4.2577173456940093e-08</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>-1.2627671837357752e-07</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>-8.6381478077392128e-09</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>-1.6167780604933552e-08</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>3.6716016806697835e-09</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>-7.6992668656127543e-09</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>-1.0506663306483304e-08</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>-1.1500420951387948e-08</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="1">
         <v>3.10852712243165e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1">
         <v>-0.016928823797744658</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-1.3370232582510152e-05</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>-1.4247455701788605e-05</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>4.8681643496100329e-05</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>-1.5669957181769654e-07</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.0023127519486284913</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>0.0016374086850153291</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>-4.9425622327013593e-05</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>-3.5390068947481085e-05</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>1.243228887934842e-05</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>1.578435119886709e-05</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>-5.6379729311195267e-06</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>-5.0393697368066861e-06</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>-2.4585706099529143e-05</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>1.885211260610844e-05</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>-1.6348940072019611e-05</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>-4.2652611416371577e-06</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>-1.9488806989787593e-05</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>1.3055497036559517e-06</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>8.7682092893838019e-06</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>1.0872016726031903e-05</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="1">
         <v>-0.0018615475259855217</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1">
         <v>-0.66327464199924724</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>-0.0002070734575412551</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>-9.2744866889093169e-06</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>3.6508751168161889e-05</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>-3.3011429192371133e-08</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>0.0016374086850153291</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>0.0057917843132336616</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>-3.5573823675969173e-05</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>-0.00011555691343650743</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>3.3264132382965937e-05</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>-0.0018426594672486406</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>3.5106079198130176e-05</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>3.1117485239214363e-05</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>1.0926654817328585e-05</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>6.7237082447746377e-05</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>-3.1559802097229917e-05</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>-1.837009242955878e-05</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>-3.7857139272513695e-05</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>-3.1187409998529212e-07</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>8.9908932588795909e-06</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>1.5869405388825303e-06</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="1">
         <v>-0.0016246341048142576</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1">
         <v>-0.00074460106836539051</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>-2.8192486626752265e-07</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>-4.1564544758147721e-07</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>-1.1049430494541221e-06</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>3.1310273507272825e-09</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>-4.9425622327013593e-05</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>-3.5573823675969173e-05</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>1.1598960587067177e-06</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>8.482665098038861e-07</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>-2.7038464294256436e-07</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>-3.5019113460016718e-07</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>1.0171378833027239e-07</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>2.1357947135228325e-07</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>1.1318368233722441e-06</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>4.9596604144195463e-07</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>2.9484659766926684e-07</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>1.402156554236685e-07</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>4.1567021664185558e-07</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>1.6420105751616004e-07</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>-8.2189758321311856e-08</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>-7.1061468984059433e-08</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="1">
         <v>3.957536164127224e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.0083027907922196536</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>3.2746175819342787e-06</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-8.475180703836633e-07</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>-7.742283137847424e-07</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-3.0598656652206113e-10</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>-3.5390068947481085e-05</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>-0.00011555691343650743</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>8.482665098038861e-07</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>2.5607656750476374e-06</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>-5.1801660876759265e-07</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>3.3979792921447639e-05</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>-2.5286524551906578e-07</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>2.4012783489742505e-07</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>1.6055418991468244e-06</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>7.690635771391729e-07</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>2.5186603282054728e-07</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>3.4250650470887307e-07</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>3.1635519468866255e-07</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>-2.2231281643970082e-08</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>7.5731863220103522e-08</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>2.8212907639864969e-07</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="1">
         <v>3.2102302119822986e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1">
         <v>-0.12581334097213734</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>5.610152960977531e-05</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>-1.1452839041791173e-06</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>-1.6461454327505156e-05</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>1.7609059308883614e-07</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>1.243228887934842e-05</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>3.3264132382965937e-05</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>-2.7038464294256436e-07</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>-5.1801660876759265e-07</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.00021513344539099953</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>-2.154347316773697e-05</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>-1.1003241669427027e-05</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>-2.5620627982495881e-05</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>-3.8261733725431268e-05</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>-3.3494466306429954e-05</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>-8.7908092292312935e-08</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>-2.5788605547136962e-06</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>-3.1782389981569291e-06</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>-1.4586076477393935e-06</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>-5.6915000533419749e-07</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>1.1392988202035329e-06</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="1">
         <v>0.0002335268881691261</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11">
+        <v>32</v>
+      </c>
+      <c r="B11" s="1">
         <v>-0.73992149913727201</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>-0.00028798624355746722</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>1.7717386314506317e-05</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>4.1890966680558335e-05</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-4.7155516041544943e-07</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>1.578435119886709e-05</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>-0.0018426594672486406</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>-3.5019113460016718e-07</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>3.3979792921447639e-05</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>-2.154347316773697e-05</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.0064281316682935222</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>-2.6324281179006172e-05</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>-2.4923294661707948e-05</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>-2.0369258022088024e-05</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>-2.1291047279558141e-05</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>-4.4533867153214928e-06</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>-5.3474186617407173e-06</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>5.0356227417880751e-06</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>5.9086447010324226e-06</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>1.4863022449862927e-05</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>-2.9832799561825716e-06</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="1">
         <v>-0.00081807227855558613</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1">
         <v>0.25119330048194866</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>-1.71730661914179e-06</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>5.5729388688274025e-06</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>6.64586002047606e-07</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>-1.1382547707090519e-08</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>-5.6379729311195267e-06</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>3.5106079198130176e-05</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>1.0171378833027239e-07</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>-2.5286524551906578e-07</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>-1.1003241669427027e-05</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>-2.6324281179006172e-05</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.0062049990043703176</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>0.0055541931064566515</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>0.0055534091558615186</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>0.0055499353670488095</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>-2.0311049399412257e-06</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-9.6076458136768871e-06</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>-5.8599790727456466e-06</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>-2.359450126322848e-06</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>-2.2555487158452894e-06</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>2.6491057034427041e-07</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="1">
         <v>-0.0055506013508315214</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1">
         <v>0.58001037454354476</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>-1.1550476274639013e-06</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>9.8198473013467286e-06</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>3.5539699259572568e-06</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-4.4724517688740138e-08</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>-5.0393697368066861e-06</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>3.1117485239214363e-05</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>2.1357947135228325e-07</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>2.4012783489742505e-07</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>-2.5620627982495881e-05</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>-2.4923294661707948e-05</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>0.0055541931064566515</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.0057010686921570696</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>0.0055599124083586301</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>0.0055579418702673151</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>2.1053436820936292e-07</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>-7.3180418517308348e-06</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>-3.3032071345128215e-06</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-1.3624820492039711e-06</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>-6.983094537601933e-06</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>-1.0398925033543431e-06</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="1">
         <v>-0.0056105793271829041</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1">
         <v>0.70773438424215807</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>6.8277621143589739e-06</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>1.6944553053267536e-05</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>5.090529931996824e-06</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>-4.2577173456940093e-08</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>-2.4585706099529143e-05</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>1.0926654817328585e-05</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>1.1318368233722441e-06</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>1.6055418991468244e-06</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>-3.8261733725431268e-05</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>-2.0369258022088024e-05</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>0.0055534091558615186</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>0.0055599124083586301</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>0.0056617265202414044</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>0.0056108466565002344</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>-2.8764592988390241e-06</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>-9.0178125487914876e-06</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>-6.8010055438198162e-06</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>1.1911831155232694e-06</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>-1.3871523640812331e-05</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>-1.2729529980994438e-05</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="1">
         <v>-0.0057178897909201144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1">
         <v>0.74286240226436306</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>-1.3458824438210889e-05</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>1.7858176055743041e-05</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>1.5245838117320466e-05</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>-1.2627671837357752e-07</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>1.885211260610844e-05</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>6.7237082447746377e-05</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>4.9596604144195463e-07</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>7.690635771391729e-07</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>-3.3494466306429954e-05</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>-2.1291047279558141e-05</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>0.0055499353670488095</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>0.0055579418702673151</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>0.0056108466565002344</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>0.0059057228364799274</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>2.4646513588453688e-06</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>-1.3037310947321823e-06</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>-6.1723231701483105e-06</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>8.3425362810850192e-06</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>-1.7003450962586297e-05</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>-1.3307683970525767e-05</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="1">
         <v>-0.0060237244446465395</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1">
         <v>0.055683583537217252</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>7.1818334577563201e-06</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>1.5673150154315448e-06</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>3.7839968996792708e-07</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>-8.6381478077392128e-09</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>-1.6348940072019611e-05</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>-3.1559802097229917e-05</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>2.9484659766926684e-07</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>2.5186603282054728e-07</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>-8.7908092292312935e-08</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>-4.4533867153214928e-06</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>-2.0311049399412257e-06</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>2.1053436820936292e-07</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>-2.8764592988390241e-06</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>2.4646513588453688e-06</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.0004586320147963743</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>0.00021688548699794105</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>0.00021741117687469486</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>0.00021683801904120211</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>-7.3514637901213823e-06</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>-1.1442441401139453e-05</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="1">
         <v>-0.00020977451656733082</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17">
+        <v>38</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.054989273518604831</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>4.5567919783054414e-06</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>-8.5989562211687659e-08</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>1.1426837785570177e-06</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>-1.6167780604933552e-08</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>-4.2652611416371577e-06</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>-1.837009242955878e-05</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>1.402156554236685e-07</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>3.4250650470887307e-07</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>-2.5788605547136962e-06</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>-5.3474186617407173e-06</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-9.6076458136768871e-06</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>-7.3180418517308348e-06</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>-9.0178125487914876e-06</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>-1.3037310947321823e-06</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>0.00021688548699794105</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.00058770750659732716</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>0.00021656629757566697</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>0.00021672258476286075</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>-5.0622479494116917e-06</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>-6.644645067194394e-06</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="1">
         <v>-0.00022381820919948378</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18">
+        <v>39</v>
+      </c>
+      <c r="B18" s="1">
         <v>0.0069867102623364149</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>2.1398457000646714e-06</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>-1.2084758536620781e-07</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>-6.8579926141857746e-07</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>3.6716016806697835e-09</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-1.9488806989787593e-05</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>-3.7857139272513695e-05</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>4.1567021664185558e-07</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>3.1635519468866255e-07</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>-3.1782389981569291e-06</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>5.0356227417880751e-06</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>-5.8599790727456466e-06</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>-3.3032071345128215e-06</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>-6.8010055438198162e-06</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>-6.1723231701483105e-06</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>0.00021741117687469486</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>0.00021656629757566697</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.00043890971732963956</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>0.00021665878684070308</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>-6.8311898968875335e-06</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>-7.9448477780293311e-06</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="1">
         <v>-0.00018288754119552832</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19">
+        <v>40</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.036456692632002921</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>-1.9323207073742462e-06</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>5.3632019535039189e-06</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>4.5814455026578871e-07</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>-7.6992668656127543e-09</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>1.3055497036559517e-06</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>-3.1187409998529212e-07</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>1.6420105751616004e-07</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>-2.2231281643970082e-08</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>-1.4586076477393935e-06</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>5.9086447010324226e-06</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>-2.359450126322848e-06</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>-1.3624820492039711e-06</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>1.1911831155232694e-06</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>8.3425362810850192e-06</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>0.00021683801904120211</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>0.00021672258476286075</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>0.00021665878684070308</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.00030961848922483534</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>-8.3027524427428102e-06</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>-1.1271628256927445e-05</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="1">
         <v>-0.0002270930204841361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20">
+        <v>41</v>
+      </c>
+      <c r="B20" s="1">
         <v>-0.041281765754247413</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>6.5720317889360439e-06</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>5.3034535509519079e-06</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>6.3199444070117016e-07</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>-1.0506663306483304e-08</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>8.7682092893838019e-06</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>8.9908932588795909e-06</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>-8.2189758321311856e-08</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>7.5731863220103522e-08</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>-5.6915000533419749e-07</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>1.4863022449862927e-05</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>-2.2555487158452894e-06</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>-6.983094537601933e-06</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-1.3871523640812331e-05</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>-1.7003450962586297e-05</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>-7.3514637901213823e-06</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>-5.0622479494116917e-06</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>-6.8311898968875335e-06</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>-8.3027524427428102e-06</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.0006007989595596231</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>4.4427835339549295e-05</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="1">
         <v>-3.6730758495516343e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21">
+        <v>42</v>
+      </c>
+      <c r="B21" s="1">
         <v>0.016497149622113592</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>1.2437030710985219e-06</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>2.7105214198764388e-07</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>5.1308609260046722e-07</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>-1.1500420951387948e-08</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>1.0872016726031903e-05</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>1.5869405388825303e-06</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>-7.1061468984059433e-08</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>2.8212907639864969e-07</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>1.1392988202035329e-06</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>-2.9832799561825716e-06</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>2.6491057034427041e-07</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>-1.0398925033543431e-06</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>-1.2729529980994438e-05</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>-1.3307683970525767e-05</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>-1.1442441401139453e-05</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>-6.644645067194394e-06</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>-7.9448477780293311e-06</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>-1.1271628256927445e-05</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>4.4427835339549295e-05</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>0.00068547544206582758</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>-3.0815456541852312e-05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1">
         <v>-1.9417297530504412</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>-0.0011787406646399177</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>-0.00021467551396000859</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>-0.00032147168797014053</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>3.10852712243165e-06</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>-0.0018615475259855217</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>-0.0016246341048142576</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>3.957536164127224e-05</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>3.2102302119822986e-05</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0.0002335268881691261</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>-0.00081807227855558613</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>-0.0055506013508315214</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>-0.0056105793271829041</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>-0.0057178897909201144</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>-0.0060237244446465395</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>-0.00020977451656733082</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="1">
         <v>-0.00022381820919948378</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <v>-0.00018288754119552832</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <v>-0.0002270930204841361</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="1">
         <v>-3.6730758495516343e-05</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="1">
         <v>-3.0815456541852312e-05</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>0.013506353313803888</v>
       </c>
     </row>
@@ -1986,1563 +1910,1563 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1">
         <v>-1.8255849224240093</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0.001057206644152982</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>0.00011507870190120423</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>4.1886240909560413e-05</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>-4.1614432661951152e-07</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-1.4292707515829647e-05</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>-0.00011367381139064172</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>-2.445916677268429e-07</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>1.5880899310935888e-06</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>3.2031465941972395e-05</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>-0.0002028688866052117</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>-8.3672215277185422e-06</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>-2.9541037619877164e-07</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>7.7514538181741349e-06</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>-5.4307492754953886e-06</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>1.8590968170153935e-06</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>-3.6371956335133894e-06</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>-3.2537820098731685e-07</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>-2.7583573081911383e-06</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>6.9847315780087009e-06</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>6.4333479333806854e-06</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="1">
         <v>-0.0010411481793853906</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1">
         <v>-2.4308000294255381</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>0.00011507870190120423</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.00021109181794735129</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>8.3589480787488363e-06</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>-9.037669816121977e-08</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>-8.5474136361048242e-06</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>-1.8781362392590412e-05</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>-5.7290154050850853e-07</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>-6.9496580589979512e-07</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>3.5465216935381476e-05</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>3.0432016711066988e-06</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>-2.4560988700669643e-06</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>6.8047951943197996e-06</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>2.1376992407220631e-05</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>2.5282221458698039e-05</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>7.2885553862286698e-06</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>4.9882889769430729e-06</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>5.4369172694482569e-06</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>7.9830935377976852e-06</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>8.4992917610273144e-06</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>1.5819244054425819e-07</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>-0.00025763925313880662</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1">
         <v>0.091232225114716736</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>4.1886240909560413e-05</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>8.3589480787488363e-06</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>1.2583700705643229e-05</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>-1.2061477984888593e-07</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>6.3256020640278121e-05</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>6.615666207889817e-05</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>-1.372990996460647e-06</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>-1.3907963087071302e-06</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>-1.5668885783856189e-05</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>3.3464320450340095e-05</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>-3.1045066785336591e-07</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>2.7540728103072975e-06</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>3.3757347656099691e-06</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>1.3746973963612181e-05</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>2.541007309070153e-07</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>-5.5379705113632243e-07</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>-7.7598682383934529e-07</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>-3.434549542771721e-07</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>1.2793033028365857e-06</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>1.3972192003860049e-06</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="1">
         <v>-0.00029543313338156052</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1">
         <v>-0.0012987205359832371</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>-4.1614432661951152e-07</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>-9.037669816121977e-08</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>-1.2061477984888593e-07</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>1.2675145811938677e-09</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>-2.0436234842304807e-07</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>-2.4294508692290487e-07</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>4.0983604885616014e-09</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>4.3720991428813072e-09</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>1.2931063771148347e-07</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-3.5391897599161302e-07</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>9.0977288371947249e-10</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-3.6653168000817868e-08</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-2.3317898750943807e-08</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>-1.0539426160107154e-07</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>-7.2400756345057747e-09</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>1.5212372990398306e-09</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>6.5972285880916096e-09</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>3.9884111816728617e-09</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>-1.3689580615296676e-08</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>-1.6934582707039191e-08</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="1">
         <v>2.5990650886798615e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1">
         <v>0.28823065726993963</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-1.4292707515829647e-05</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>-8.5474136361048242e-06</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>6.3256020640278121e-05</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>-2.0436234842304807e-07</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.0028308144986690146</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>0.0022672653898124415</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>-5.7220562904653971e-05</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>-4.5947612446113273e-05</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>3.1495199078912652e-05</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>5.5896704970519049e-05</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>-4.5555655351058868e-06</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>-1.2289690099272286e-05</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>-1.9746132825861919e-05</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>2.6920731872055953e-05</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>-1.1553280007418547e-05</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>-7.0302348549560584e-06</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>-1.2618457290065576e-05</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>2.5815818518798024e-06</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>2.2030690569090536e-05</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>3.0303761633646109e-05</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="1">
         <v>-0.0025746405134800428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1">
         <v>-0.30895560836049207</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>-0.00011367381139064172</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>-1.8781362392590412e-05</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>6.615666207889817e-05</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>-2.4294508692290487e-07</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>0.0022672653898124415</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>0.0046472677165175936</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>-4.6086432521688724e-05</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>-9.2444045724612462e-05</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>3.7818698022865131e-05</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>-0.0010290360829635231</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>1.8276027644303743e-05</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>6.185487339301749e-06</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>1.7184152535628175e-06</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>6.1912067113460852e-05</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>-3.5655712080569887e-05</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>-1.331648359566989e-05</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>-2.8010000503152009e-05</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>1.0887254568779135e-05</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>2.1991553895811118e-05</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>1.5739324766953561e-05</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="1">
         <v>-0.0026376700541694631</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1">
         <v>-0.00091723392407469962</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>-2.445916677268429e-07</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>-5.7290154050850853e-07</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>-1.372990996460647e-06</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>4.0983604885616014e-09</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>-5.7220562904653971e-05</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>-4.6086432521688724e-05</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>1.2738223397937086e-06</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>1.0305957349852983e-06</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>-4.5119142323026414e-07</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>-1.0841240345890149e-06</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>9.0680537311187045e-08</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>4.3117206054127361e-07</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>1.0357878243169625e-06</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>4.054333942960814e-07</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>7.646008668634707e-08</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>1.5378920878922871e-07</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>1.2371119953324255e-07</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>-7.4631133613091613e-09</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>-3.8239036309664367e-07</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>-4.969478621604789e-07</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="1">
         <v>5.1878049811282039e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.0077526427736544778</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>1.5880899310935888e-06</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-6.9496580589979512e-07</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>-1.3907963087071302e-06</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>4.3720991428813072e-09</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>-4.5947612446113273e-05</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>-9.2444045724612462e-05</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>1.0305957349852983e-06</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>2.0781051112200012e-06</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>-6.3142670034631226e-08</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>1.8697737449558651e-05</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>-4.6999486146770411e-07</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>1.9920129585787399e-07</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>9.4396245373214039e-07</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>1.2370902895632763e-07</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>3.2631929854776654e-07</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>2.0087264595040224e-07</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>6.5520712019059521e-08</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>-5.4160714656389727e-07</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>-2.8171428609558929e-07</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>-8.5060405448936576e-08</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="1">
         <v>5.2047273482500377e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.095694310140127664</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>3.2031465941972395e-05</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>3.5465216935381476e-05</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>-1.5668885783856189e-05</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>1.2931063771148347e-07</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>3.1495199078912652e-05</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>3.7818698022865131e-05</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>-4.5119142323026414e-07</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>-6.3142670034631226e-08</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.00027035153362456159</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>-4.5860397607863414e-05</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>-3.4823548222216852e-06</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>-1.2198678220872903e-05</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>-1.6206316795931393e-05</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>-1.2958358751100475e-05</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>3.2195709866802505e-06</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>3.9603052686514158e-06</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>-2.6921025199997318e-06</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>3.3290214807585483e-06</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>1.6235191823966083e-06</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>4.7047985687512794e-06</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="1">
         <v>0.00023002689777709158</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11">
+        <v>32</v>
+      </c>
+      <c r="B11" s="1">
         <v>-0.90994252932839303</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>-0.0002028688866052117</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>3.0432016711066988e-06</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>3.3464320450340095e-05</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-3.5391897599161302e-07</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>5.5896704970519049e-05</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>-0.0010290360829635231</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>-1.0841240345890149e-06</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>1.8697737449558651e-05</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>-4.5860397607863414e-05</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.0037353566661563909</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>-9.4595958747498165e-06</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>-5.4620722450963218e-06</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>-3.2109062575558342e-06</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>-9.6176024800112602e-06</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>-4.7657325556950621e-06</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>-1.3305954227985676e-06</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>-2.7994984306380289e-07</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>7.1481590243151225e-07</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>1.6850774506966214e-05</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>-3.5663275397405314e-06</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="1">
         <v>-0.0006852115663035439</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1">
         <v>0.33194293025969268</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>-8.3672215277185422e-06</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>-2.4560988700669643e-06</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>-3.1045066785336591e-07</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>9.0977288371947249e-10</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>-4.5555655351058868e-06</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>1.8276027644303743e-05</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>9.0680537311187045e-08</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>-4.6999486146770411e-07</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>-3.4823548222216852e-06</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>-9.4595958747498165e-06</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.0043469827515401748</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>0.0038378490678665274</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>0.0038348185842087624</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>0.0038321055238737158</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>2.6616739842232702e-07</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>5.5321817700697539e-06</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>3.011415133080454e-06</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>-1.9426482138538932e-06</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>-7.2542343928769969e-07</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>1.3331343587874293e-05</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="1">
         <v>-0.0038203713465566479</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1">
         <v>0.76461666460759692</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>-2.9541037619877164e-07</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>6.8047951943197996e-06</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>2.7540728103072975e-06</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-3.6653168000817868e-08</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>-1.2289690099272286e-05</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>6.185487339301749e-06</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>4.3117206054127361e-07</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>1.9920129585787399e-07</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>-1.2198678220872903e-05</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>-5.4620722450963218e-06</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>0.0038378490678665274</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.0039816713661754597</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>0.0038380073841052615</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>0.0038363880127517502</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>4.7081821256351802e-06</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>5.6218441170808594e-06</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>1.446629381185216e-06</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-9.3542801339880201e-07</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>-3.9459845709262158e-07</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>7.428903411569461e-06</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="1">
         <v>-0.0038820052544547828</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1">
         <v>0.94560570623606321</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>7.7514538181741349e-06</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>2.1376992407220631e-05</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>3.3757347656099691e-06</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>-2.3317898750943807e-08</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>-1.9746132825861919e-05</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>1.7184152535628175e-06</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>1.0357878243169625e-06</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>9.4396245373214039e-07</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>-1.6206316795931393e-05</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>-3.2109062575558342e-06</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>0.0038348185842087624</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>0.0038380073841052615</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>0.0039427219275658077</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>0.0038869931193062255</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>9.283035588648008e-06</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>8.0963030703885402e-06</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>3.9217146705373002e-06</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>6.0054168547804787e-06</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>-7.8749453258989025e-06</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>-3.9049985380980342e-06</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="1">
         <v>-0.0039834841485284801</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1">
         <v>0.95023976615731609</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>-5.4307492754953886e-06</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>2.5282221458698039e-05</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>1.3746973963612181e-05</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>-1.0539426160107154e-07</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>2.6920731872055953e-05</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>6.1912067113460852e-05</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>4.054333942960814e-07</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>1.2370902895632763e-07</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>-1.2958358751100475e-05</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>-9.6176024800112602e-06</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>0.0038321055238737158</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>0.0038363880127517502</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>0.0038869931193062255</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>0.0041702847986030602</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>1.0624777324740855e-05</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>1.38561027018929e-05</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>3.1650546156481189e-06</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>8.847417053660004e-06</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>-7.6549979652008117e-06</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>-1.1356415467249767e-06</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="1">
         <v>-0.0043085648096578806</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1">
         <v>0.058337441801803606</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>1.8590968170153935e-06</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>7.2885553862286698e-06</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>2.541007309070153e-07</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>-7.2400756345057747e-09</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>-1.1553280007418547e-05</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>-3.5655712080569887e-05</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>7.646008668634707e-08</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>3.2631929854776654e-07</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>3.2195709866802505e-06</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>-4.7657325556950621e-06</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>2.6616739842232702e-07</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>4.7081821256351802e-06</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>9.283035588648008e-06</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>1.0624777324740855e-05</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.00047392632466527302</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>0.00022367705007798083</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>0.00022401163539705328</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>0.00022376499026664323</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>-9.4661770850943712e-06</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>-1.0575193670347042e-05</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="1">
         <v>-0.00022094426445912121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17">
+        <v>38</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.032576907432431246</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>-3.6371956335133894e-06</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>4.9882889769430729e-06</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>-5.5379705113632243e-07</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>1.5212372990398306e-09</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>-7.0302348549560584e-06</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>-1.331648359566989e-05</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>1.5378920878922871e-07</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>2.0087264595040224e-07</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>3.9603052686514158e-06</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>-1.3305954227985676e-06</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>5.5321817700697539e-06</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>5.6218441170808594e-06</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>8.0963030703885402e-06</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>1.38561027018929e-05</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>0.00022367705007798083</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.00059639784398684615</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>0.00022317781266167051</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>0.00022335734252743646</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>-7.4721834193413605e-06</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>-8.6427431271359002e-06</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="1">
         <v>-0.00021191285393747645</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18">
+        <v>39</v>
+      </c>
+      <c r="B18" s="1">
         <v>-0.0055055550093970045</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>-3.2537820098731685e-07</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>5.4369172694482569e-06</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>-7.7598682383934529e-07</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>6.5972285880916096e-09</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-1.2618457290065576e-05</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>-2.8010000503152009e-05</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>1.2371119953324255e-07</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>6.5520712019059521e-08</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>-2.6921025199997318e-06</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>-2.7994984306380289e-07</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>3.011415133080454e-06</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>1.446629381185216e-06</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>3.9217146705373002e-06</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>3.1650546156481189e-06</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>0.00022401163539705328</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>0.00022317781266167051</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.00044872356332991618</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>0.00022367953741975812</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>-8.2476925068708214e-06</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>-6.6459852256753221e-06</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="1">
         <v>-0.00019744945336314001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19">
+        <v>40</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.017840644512959011</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>-2.7583573081911383e-06</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>7.9830935377976852e-06</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>-3.434549542771721e-07</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>3.9884111816728617e-09</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>2.5815818518798024e-06</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>1.0887254568779135e-05</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>-7.4631133613091613e-09</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>-5.4160714656389727e-07</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>3.3290214807585483e-06</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>7.1481590243151225e-07</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>-1.9426482138538932e-06</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>-9.3542801339880201e-07</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>6.0054168547804787e-06</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>8.847417053660004e-06</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>0.00022376499026664323</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>0.00022335734252743646</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>0.00022367953741975812</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.00031720741760114541</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>-8.1226831786066678e-06</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>-1.2628995164168324e-05</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="1">
         <v>-0.00022419860034122966</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20">
+        <v>41</v>
+      </c>
+      <c r="B20" s="1">
         <v>-0.064242499184584606</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>6.9847315780087009e-06</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>8.4992917610273144e-06</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>1.2793033028365857e-06</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>-1.3689580615296676e-08</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>2.2030690569090536e-05</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>2.1991553895811118e-05</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>-3.8239036309664367e-07</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>-2.8171428609558929e-07</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>1.6235191823966083e-06</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>1.6850774506966214e-05</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>-7.2542343928769969e-07</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>-3.9459845709262158e-07</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-7.8749453258989025e-06</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>-7.6549979652008117e-06</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>-9.4661770850943712e-06</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>-7.4721834193413605e-06</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>-8.2476925068708214e-06</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>-8.1226831786066678e-06</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.00061924828442406533</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>4.4868931024314377e-05</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="1">
         <v>-6.6422780296909601e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21">
+        <v>42</v>
+      </c>
+      <c r="B21" s="1">
         <v>0.016842952586390181</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>6.4333479333806854e-06</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>1.5819244054425819e-07</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>1.3972192003860049e-06</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>-1.6934582707039191e-08</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>3.0303761633646109e-05</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>1.5739324766953561e-05</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>-4.969478621604789e-07</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>-8.5060405448936576e-08</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>4.7047985687512794e-06</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>-3.5663275397405314e-06</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>1.3331343587874293e-05</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>7.428903411569461e-06</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>-3.9049985380980342e-06</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>-1.1356415467249767e-06</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>-1.0575193670347042e-05</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>-8.6427431271359002e-06</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>-6.6459852256753221e-06</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>-1.2628995164168324e-05</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>4.4868931024314377e-05</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>0.00068806027690791174</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>-7.0092403777709529e-05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1">
         <v>-0.92010098884798619</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>-0.0010411481793853906</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>-0.00025763925313880662</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>-0.00029543313338156052</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>2.5990650886798615e-06</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>-0.0025746405134800428</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>-0.0026376700541694631</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>5.1878049811282039e-05</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>5.2047273482500377e-05</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0.00023002689777709158</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>-0.0006852115663035439</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>-0.0038203713465566479</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>-0.0038820052544547828</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>-0.0039834841485284801</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>-0.0043085648096578806</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>-0.00022094426445912121</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="1">
         <v>-0.00021191285393747645</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <v>-0.00019744945336314001</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <v>-0.00022419860034122966</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="1">
         <v>-6.6422780296909601e-05</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="1">
         <v>-7.0092403777709529e-05</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>0.011813911367619388</v>
       </c>
     </row>
@@ -3557,1301 +3481,1301 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="B2" s="1">
         <v>0.20430635043939593</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>2.8881560645154346e-05</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>-3.0509024891363889e-07</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>8.6099626555217828e-05</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>4.8425192880475451e-05</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-1.973794133327968e-06</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>-1.0215058666028916e-06</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>-3.408809588793632e-05</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>0.00015413787720509013</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>-2.2930870948608295e-06</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>-7.9783257222451011e-07</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>2.3248862606874173e-06</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>2.2825625335801146e-05</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>1.9128672309603612e-06</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>2.9170513795964098e-06</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>-6.5495661217632243e-07</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>1.320416608560091e-06</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>-2.8033648846005308e-07</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>-1.8662419111393569e-07</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-0.0006091087699202465</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1">
         <v>-0.0023212928418990886</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>-3.0509024891363889e-07</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>3.4065502308447995e-09</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-2.8307746436871877e-07</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>1.4141748540246992e-07</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>5.7429981046954551e-09</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>-4.8538884863747281e-09</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>3.6521717373354578e-07</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>-1.7050555238381949e-06</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>1.6644389251726917e-08</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>1.6042470441065332e-09</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>2.4658780555001307e-09</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>-1.6773357255421797e-07</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>-3.0911110908537161e-08</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>-3.6523999647550355e-08</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>3.2092389339022034e-11</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>-1.9893730686702269e-08</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>-8.1515703051772965e-09</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>-1.0542444914742789e-08</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>6.0683271786420401e-06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1">
         <v>-0.066832827882654003</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>8.6099626555217828e-05</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-2.8307746436871877e-07</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>0.0043568689473529564</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>0.0027669991110117233</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>-9.4184432180944398e-05</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>-6.1309006234216369e-05</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>4.2723678355002329e-05</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>1.473826881517439e-05</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>-4.060093278096059e-05</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>-5.5505028596456987e-05</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>-8.0719046118051812e-05</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>1.5424399083184553e-05</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>-3.7911295995306231e-05</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>1.2500778561052997e-05</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>-2.5835141003411376e-05</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>1.5298650522212278e-05</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>2.3469024313683491e-05</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>1.5705401189065184e-05</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>-0.0032241595934243581</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1">
         <v>-0.48778301582995509</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>4.8425192880475451e-05</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>1.4141748540246992e-07</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>0.0027669991110117233</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.018271671830755145</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>-6.1493778633430154e-05</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>-0.00035998593180084786</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>8.5279550448687032e-05</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>-0.0071165611334957019</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>-4.7518193915697459e-05</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-0.00011908465754683828</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>-0.00015348084976945953</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-1.1685665546985241e-05</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-0.00012686572723581306</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>-1.5826095606651797e-05</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>-6.8306274111191366e-05</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>-1.4991369448112792e-06</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>2.9450385409217396e-05</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>-3.632351937970049e-06</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>-0.0023967617664365777</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1">
         <v>-0.0017565090522708986</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-1.973794133327968e-06</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>5.7429981046954551e-09</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>-9.4184432180944398e-05</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>-6.1493778633430154e-05</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>2.2143938075225872e-06</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>1.4875956754883795e-06</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>-8.4219944307167799e-07</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>-4.6118895614210189e-07</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>1.011725665827227e-06</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>1.4481860550254392e-06</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>2.8629477860033014e-06</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>1.3666174125926817e-06</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>7.3644297525860497e-07</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>-1.204667951896446e-07</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>5.8686725216386292e-07</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>9.1195243836625382e-09</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>-2.5772874440150374e-07</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>2.9985213865470067e-08</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>6.8999087943364079e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1">
         <v>0.0040844188037978792</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>-1.0215058666028916e-06</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>-4.8538884863747281e-09</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>-6.1309006234216369e-05</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>-0.00035998593180084786</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>1.4875956754883795e-06</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>7.665305840977715e-06</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>-1.6743792884877403e-06</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>0.00013303432099094297</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>2.9356245040857602e-06</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>5.3096828244392244e-06</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>7.7773287076433157e-06</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>5.5451268230999754e-06</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>1.8969791271524452e-06</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>3.8937068537555693e-07</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>6.2352051071293473e-07</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>-1.5822716549813978e-07</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>-3.3134894233467166e-08</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>6.5345565718488394e-07</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>4.5238948461371328e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8">
+        <v>31</v>
+      </c>
+      <c r="B8" s="1">
         <v>-0.16388386414656197</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>-3.408809588793632e-05</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>3.6521717373354578e-07</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>4.2723678355002329e-05</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>8.5279550448687032e-05</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>-8.4219944307167799e-07</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>-1.6743792884877403e-06</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>0.00041392343652519426</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>1.3891988404492365e-05</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>-1.1601664228600373e-05</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>-3.2047240153823653e-05</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>-4.7779601704832468e-05</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>-3.6664520150739029e-05</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>-3.1421661813252177e-06</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>-5.4910006741577592e-06</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>-1.101444223766341e-05</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>-7.5423102284694918e-06</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>1.7512970727154119e-06</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>5.3996079957391269e-07</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>0.0004753088342797833</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.38979868611764235</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.00015413787720509013</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-1.7050555238381949e-06</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>1.473826881517439e-05</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-0.0071165611334957019</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>-4.6118895614210189e-07</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>0.00013303432099094297</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>1.3891988404492365e-05</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.068002816000445859</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>-3.0881269994551691e-05</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>-8.0316372740493251e-06</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>-2.6774907538087196e-05</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>0.00010522370618964733</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>-0.00014833285237439114</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>-0.00011867298742927319</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>-9.2769616292634051e-05</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>-2.5909212177859581e-05</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>1.8354366801177469e-05</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>7.0301051936679109e-05</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>-0.0031791273987641722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.40879718168408136</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>-2.2930870948608295e-06</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>1.6644389251726917e-08</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>-4.060093278096059e-05</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>-4.7518193915697459e-05</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>1.011725665827227e-06</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>2.9356245040857602e-06</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>-1.1601664228600373e-05</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>-3.0881269994551691e-05</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.012430687203216936</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>0.01113056101172144</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>0.011136670651677767</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>0.011135154047603445</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>1.2800263005368043e-05</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>-1.0516665044224181e-05</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>4.8520006408806382e-06</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>2.9574480762937567e-06</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>-1.6608086082453924e-05</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>1.4004557969079399e-05</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>-0.011071622803303234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1">
         <v>0.75216946137045837</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>-7.9783257222451011e-07</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>1.6042470441065332e-09</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>-5.5505028596456987e-05</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-0.00011908465754683828</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>1.4481860550254392e-06</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>5.3096828244392244e-06</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>-3.2047240153823653e-05</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>-8.0316372740493251e-06</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0.01113056101172144</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.011421691940548441</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>0.011152598390116092</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>0.011154577401756864</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>5.5933171758882238e-06</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>-1.2861251581431976e-05</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>-2.9429622776718402e-06</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>-8.1661870762146652e-06</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>-2.4242718215907665e-05</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>1.2860226054025558e-05</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>-0.011102692043062532</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1">
         <v>0.91837066803853729</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>2.3248862606874173e-06</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>2.4658780555001307e-09</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>-8.0719046118051812e-05</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>-0.00015348084976945953</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>2.8629477860033014e-06</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>7.7773287076433157e-06</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>-4.7779601704832468e-05</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>-2.6774907538087196e-05</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0.011136670651677767</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>0.011152598390116092</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.011342254252106049</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>0.011250107902777699</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>5.7769424436609386e-07</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>-1.6869341585141643e-05</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>-1.1791361975953808e-05</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-3.4546508441578303e-06</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>-3.6098632793938253e-05</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>-9.9539573748057135e-06</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>-0.011305248179120309</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1">
         <v>0.99206529000175603</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>2.2825625335801146e-05</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>-1.6773357255421797e-07</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>1.5424399083184553e-05</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-1.1685665546985241e-05</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>1.3666174125926817e-06</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>5.5451268230999754e-06</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>-3.6664520150739029e-05</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>0.00010522370618964733</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>0.011135154047603445</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>0.011154577401756864</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>0.011250107902777699</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.011828270974888521</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>1.2691574107193544e-05</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>3.8801738764868525e-07</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>-8.9499357715685572e-06</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>1.4831262213409532e-05</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>-3.8708207360347469e-05</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-1.561592222473132e-05</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>-0.011925467328839791</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1">
         <v>0.078891736268951781</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>1.9128672309603612e-06</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>-3.0911110908537161e-08</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>-3.7911295995306231e-05</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>-0.00012686572723581306</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>7.3644297525860497e-07</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>1.8969791271524452e-06</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>-3.1421661813252177e-06</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>-0.00014833285237439114</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>1.2800263005368043e-05</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>5.5933171758882238e-06</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>5.7769424436609386e-07</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>1.2691574107193544e-05</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>0.00092013163067375641</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>0.00043035530085818743</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>0.00043113705121879537</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>0.00043048457062963964</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>-1.3971070506884658e-05</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>-2.5715980704856164e-05</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>-0.0004436507594232725</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1">
         <v>-0.021845009186522536</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>2.9170513795964098e-06</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>-3.6523999647550355e-08</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>1.2500778561052997e-05</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>-1.5826095606651797e-05</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>-1.204667951896446e-07</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>3.8937068537555693e-07</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>-5.4910006741577592e-06</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>-0.00011867298742927319</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>-1.0516665044224181e-05</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>-1.2861251581431976e-05</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>-1.6869341585141643e-05</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>3.8801738764868525e-07</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>0.00043035530085818743</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>0.0011245222538724892</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>0.00042960428036948359</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>0.00043056527678344262</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>-1.2237119585095988e-05</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>-1.5868528411888994e-05</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>-0.00046721464011353518</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1">
         <v>-0.033808010242560541</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>-6.5495661217632243e-07</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>3.2092389339022034e-11</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>-2.5835141003411376e-05</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>-6.8306274111191366e-05</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>5.8686725216386292e-07</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>6.2352051071293473e-07</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-1.101444223766341e-05</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>-9.2769616292634051e-05</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>4.8520006408806382e-06</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>-2.9429622776718402e-06</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>-1.1791361975953808e-05</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>-8.9499357715685572e-06</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>0.00043113705121879537</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>0.00042960428036948359</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.00086278510898568455</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>0.00043025857177193447</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>-9.792970691213109e-06</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>-1.5905851509414938e-05</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>-0.00038116891736110915</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.0043684736906636533</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>1.320416608560091e-06</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>-1.9893730686702269e-08</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>1.5298650522212278e-05</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>-1.4991369448112792e-06</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>9.1195243836625382e-09</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>-1.5822716549813978e-07</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>-7.5423102284694918e-06</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>-2.5909212177859581e-05</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>2.9574480762937567e-06</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>-8.1661870762146652e-06</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-3.4546508441578303e-06</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>1.4831262213409532e-05</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>0.00043048457062963964</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>0.00043056527678344262</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>0.00043025857177193447</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.0006027111247811209</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>-1.2063151243967101e-05</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>-2.5442128584490164e-05</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>-0.00044626935011963078</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18">
+        <v>41</v>
+      </c>
+      <c r="B18" s="1">
         <v>-0.1837534696494359</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>-2.8033648846005308e-07</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>-8.1515703051772965e-09</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>2.3469024313683491e-05</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>2.9450385409217396e-05</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-2.5772874440150374e-07</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>-3.3134894233467166e-08</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>1.7512970727154119e-06</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>1.8354366801177469e-05</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>-1.6608086082453924e-05</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>-2.4242718215907665e-05</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>-3.6098632793938253e-05</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>-3.8708207360347469e-05</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>-1.3971070506884658e-05</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>-1.2237119585095988e-05</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>-9.792970691213109e-06</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>-1.2063151243967101e-05</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.00099160000164478113</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>8.6995458354472463e-05</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>-2.2370861568370149e-05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1">
         <v>-0.059828760422057779</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>-1.8662419111393569e-07</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>-1.0542444914742789e-08</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>1.5705401189065184e-05</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>-3.632351937970049e-06</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>2.9985213865470067e-08</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>6.5345565718488394e-07</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>5.3996079957391269e-07</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>7.0301051936679109e-05</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>1.4004557969079399e-05</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>1.2860226054025558e-05</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>-9.9539573748057135e-06</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>-1.561592222473132e-05</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>-2.5715980704856164e-05</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>-1.5868528411888994e-05</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>-1.5905851509414938e-05</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>-2.5442128584490164e-05</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>8.6995458354472463e-05</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.0012448567601905883</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>-4.3721998220917082e-05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20">
+        <v>43</v>
+      </c>
+      <c r="B20" s="1">
         <v>-3.3544805095092332</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-0.0006091087699202465</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>6.0683271786420401e-06</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>-0.0032241595934243581</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>-0.0023967617664365777</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>6.8999087943364079e-05</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>4.5238948461371328e-05</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>0.0004753088342797833</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>-0.0031791273987641722</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>-0.011071622803303234</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>-0.011102692043062532</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>-0.011305248179120309</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>-0.011925467328839791</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-0.0004436507594232725</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>-0.00046721464011353518</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>-0.00038116891736110915</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>-0.00044626935011963078</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>-2.2370861568370149e-05</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>-4.3721998220917082e-05</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.025501035053476308</v>
       </c>
     </row>
@@ -4866,1301 +4790,1301 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="B2" s="1">
         <v>0.12920302377790582</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>2.5471193236493935e-05</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>-2.4847491259964255e-07</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>0.000121971796287615</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>0.00013107380288478833</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-2.7345590652706127e-06</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>-2.8213752892780642e-06</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>-3.5914777356255743e-05</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>0.00010819974632464614</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>-3.6877274151130877e-06</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>-2.4188371676083042e-06</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>-4.5709260638142002e-06</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>1.5486178217082216e-05</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>1.463820976623132e-06</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>-9.5218427312213864e-07</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>-7.1953229060753955e-07</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>-4.0400134210233308e-07</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>-1.8585288366945748e-07</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>5.9263874135765773e-07</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-0.00056777032753146776</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1">
         <v>-0.0015653836462530182</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>-2.4847491259964255e-07</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>2.6307100373215537e-09</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-4.3697476908159422e-07</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>-5.3440108711372745e-07</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>9.6652251590732571e-09</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>1.0536072191148814e-08</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>3.2381566266126347e-07</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>-1.1431102054071088e-06</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>3.5934992415473129e-08</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>1.4386073768129332e-08</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>7.6004762760813458e-08</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>-8.8334773255498052e-08</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>-2.6698565848075357e-08</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>4.0598578895961257e-09</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>5.4683378838843965e-09</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>5.2874271257048014e-09</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>2.7037140029538049e-09</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>-1.2858890292298362e-08</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>5.0894016828351108e-06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1">
         <v>0.12289913379800185</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>0.000121971796287615</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-4.3697476908159422e-07</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>0.0052423072403795842</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>0.0040716161590135672</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>-0.00010739367287276882</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>-8.3889941657866994e-05</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>2.5606533217197367e-05</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>0.0002202048157159713</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>-2.8989812308086812e-05</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>-6.2390120934371882e-05</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>-8.9373217017108561e-05</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>-2.9087620074570372e-05</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>-2.7808077606446021e-05</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>-5.8319314901317074e-07</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>-8.1148712495594824e-06</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>1.3319684304185728e-05</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>4.874643131600438e-05</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>2.4868477724590087e-05</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>-0.0047529200038380773</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1">
         <v>-0.31003370427584703</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>0.00013107380288478833</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>-5.3440108711372745e-07</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>0.0040716161590135672</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.01159192833888229</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>-8.4151373640858556e-05</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>-0.00023028885256126157</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>4.0386685600332416e-05</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>-0.0038918807374408058</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>-1.6346071705053573e-05</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-8.4236321736393818e-05</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>-0.00010289168667247024</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-1.3292708894467664e-05</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-8.2954319124720199e-05</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>-1.8206463783600837e-05</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>-5.9248795843067614e-05</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>2.8908864248175536e-05</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>4.6967923893606001e-05</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>1.9608496765550634e-05</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>-0.0049375891050917166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1">
         <v>-0.0028557937402376023</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-2.7345590652706127e-06</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>9.6652251590732571e-09</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>-0.00010739367287276882</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>-8.4151373640858556e-05</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>2.4096279465158402e-06</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>1.9020855276236891e-06</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>-1.8544126803789453e-07</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>-4.7735411603739849e-06</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>5.8875642496430983e-07</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>1.6094883716290177e-06</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>2.8516586320272533e-06</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>2.0917346712075742e-06</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>1.943070908942035e-07</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>-5.1613995070557338e-08</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>-1.1980131427971064e-07</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>-3.3547811862993347e-07</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>-8.0676600730643268e-07</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>-3.7787045133968205e-07</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>9.8010531083634879e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1">
         <v>0.0034156670166309014</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>-2.8213752892780642e-06</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>1.0536072191148814e-08</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>-8.3889941657866994e-05</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>-0.00023028885256126157</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>1.9020855276236891e-06</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>5.0517997010880416e-06</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>3.2285568984685592e-07</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>7.1426831572701436e-05</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>-1.2456979757368707e-07</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>1.8220628432150109e-06</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>3.2629011466356811e-06</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>2.1594756775543047e-06</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>9.9147645670361639e-07</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>2.0028586239853411e-07</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>2.8099907644149483e-07</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>-1.3523266812806435e-06</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>-5.9027145355914464e-07</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>-1.2015106032298894e-08</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>9.9549391511388215e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8">
+        <v>31</v>
+      </c>
+      <c r="B8" s="1">
         <v>0.13865227746364203</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>-3.5914777356255743e-05</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>3.2381566266126347e-07</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>2.5606533217197367e-05</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>4.0386685600332416e-05</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>-1.8544126803789453e-07</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>3.2285568984685592e-07</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>0.00046667464929325679</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>-6.7368257691158596e-05</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>4.7480534718390139e-06</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>-2.5547663466768752e-06</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>-3.7085174556275795e-06</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>6.2026853092809192e-06</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>-3.9459798898052041e-06</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>3.5574253642153883e-07</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>-1.4118395166430088e-05</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>-7.9341039184229824e-07</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>2.0062685353009225e-06</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>7.1848047657407536e-06</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>0.00056370649673035767</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1">
         <v>-0.10844205125782649</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.00010819974632464614</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-1.1431102054071088e-06</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>0.0002202048157159713</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-0.0038918807374408058</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>-4.7735411603739849e-06</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>7.1426831572701436e-05</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>-6.7368257691158596e-05</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.047015216402175833</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>-1.5326593427396851e-05</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>9.2354218813779285e-07</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>1.4362585644811147e-05</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>-5.1133377102238799e-05</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>-0.00015939161821503479</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>-4.659119665085672e-05</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>-8.6135991828837052e-05</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>-5.0048151100434593e-05</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>6.2867796367939305e-05</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>7.2870750219949015e-05</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>-0.0022434155287022039</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.34805390882598608</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>-3.6877274151130877e-06</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>3.5934992415473129e-08</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>-2.8989812308086812e-05</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>-1.6346071705053573e-05</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>5.8875642496430983e-07</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>-1.2456979757368707e-07</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>4.7480534718390139e-06</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>-1.5326593427396851e-05</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.0078106889119316982</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>0.0068622487285269493</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>0.0068618537946230794</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>0.0068595899635946686</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>1.526698012834479e-05</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>1.3951092798188432e-05</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>-1.3501636725052555e-06</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>-6.4509729703115766e-06</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>-2.8720275011006757e-06</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>4.652882090423984e-05</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>-0.0067783910479097325</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1">
         <v>0.84011267891136732</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>-2.4188371676083042e-06</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>1.4386073768129332e-08</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>-6.2390120934371882e-05</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-8.4236321736393818e-05</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>1.6094883716290177e-06</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>1.8220628432150109e-06</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>-2.5547663466768752e-06</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>9.2354218813779285e-07</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0.0068622487285269493</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.0071309062475789801</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>0.0068654042141709504</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>0.0068663055951554402</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>9.2122827142151494e-06</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>3.5750499411952266e-06</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>-1.8228010643657687e-05</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>-1.4839487897606893e-05</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>1.4648287515419824e-06</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>3.5637795246085398e-05</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>-0.0067882404363312282</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1">
         <v>1.0404622514984647</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>-4.5709260638142002e-06</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>7.6004762760813458e-08</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>-8.9373217017108561e-05</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>-0.00010289168667247024</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>2.8516586320272533e-06</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>3.2629011466356811e-06</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>-3.7085174556275795e-06</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>1.4362585644811147e-05</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0.0068618537946230794</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>0.0068654042141709504</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.0070538662067896182</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>0.0069578581109151312</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>9.4720357388651602e-06</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>1.0130478456854115e-05</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>-1.2617187267433912e-05</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-4.2701699219132902e-06</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>-1.5756447824347835e-05</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>1.6609350624722869e-05</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>-0.0068995549192295558</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1">
         <v>1.0974408470305186</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>1.5486178217082216e-05</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>-8.8334773255498052e-08</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>-2.9087620074570372e-05</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-1.3292708894467664e-05</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>2.0917346712075742e-06</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>2.1594756775543047e-06</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>6.2026853092809192e-06</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>-5.1133377102238799e-05</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>0.0068595899635946686</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>0.0068663055951554402</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>0.0069578581109151312</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.00749866335243159</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>1.150251279782033e-05</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>1.3335146621490131e-05</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>-1.4874806186960851e-05</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>5.9575624906819376e-07</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>-1.2175861309521671e-05</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>1.9082985864348929e-05</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>-0.0075117281763161419</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1">
         <v>0.045624092158088415</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>1.463820976623132e-06</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>-2.6698565848075357e-08</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>-2.7808077606446021e-05</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>-8.2954319124720199e-05</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>1.943070908942035e-07</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>9.9147645670361639e-07</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>-3.9459798898052041e-06</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>-0.00015939161821503479</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>1.526698012834479e-05</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>9.2122827142151494e-06</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>9.4720357388651602e-06</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>1.150251279782033e-05</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>0.000901195819998447</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>0.000435643274583295</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>0.00043663516235486539</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>0.00043550091840052952</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>-1.6420196828498262e-05</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>-2.5394861157167082e-05</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>-0.0004289266914254419</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1">
         <v>-0.054680517584804376</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>-9.5218427312213864e-07</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>4.0598578895961257e-09</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>-5.8319314901317074e-07</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>-1.8206463783600837e-05</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>-5.1613995070557338e-08</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>2.0028586239853411e-07</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>3.5574253642153883e-07</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>-4.659119665085672e-05</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>1.3951092798188432e-05</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>3.5750499411952266e-06</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>1.0130478456854115e-05</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>1.3335146621490131e-05</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>0.000435643274583295</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>0.0010934877389706676</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>0.00043507014209516416</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>0.00043498779446051784</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>-1.3139516654432279e-05</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>-2.4293263148533335e-05</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>-0.00040441706406298079</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1">
         <v>-0.060579211615807718</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>-7.1953229060753955e-07</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>5.4683378838843965e-09</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>-8.1148712495594824e-06</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>-5.9248795843067614e-05</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>-1.1980131427971064e-07</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>2.8099907644149483e-07</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-1.4118395166430088e-05</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>-8.6135991828837052e-05</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>-1.3501636725052555e-06</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>-1.8228010643657687e-05</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>-1.2617187267433912e-05</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>-1.4874806186960851e-05</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>0.00043663516235486539</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>0.00043507014209516416</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.00083837986099850404</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>0.00043579003632577542</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>-1.6782417198179557e-05</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>-1.6813507572433465e-05</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>-0.00037532611098678253</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1">
         <v>-0.015612779595930033</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>-4.0400134210233308e-07</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>5.2874271257048014e-09</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>1.3319684304185728e-05</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>2.8908864248175536e-05</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>-3.3547811862993347e-07</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>-1.3523266812806435e-06</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>-7.9341039184229824e-07</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>-5.0048151100434593e-05</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>-6.4509729703115766e-06</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>-1.4839487897606893e-05</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-4.2701699219132902e-06</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>5.9575624906819376e-07</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>0.00043550091840052952</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>0.00043498779446051784</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>0.00043579003632577542</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.00060520936676436649</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>-1.4553139778668304e-05</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>-2.5737423556484971e-05</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>-0.00041468101002394367</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18">
+        <v>41</v>
+      </c>
+      <c r="B18" s="1">
         <v>-0.14607378429774548</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>-1.8585288366945748e-07</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>2.7037140029538049e-09</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>4.874643131600438e-05</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>4.6967923893606001e-05</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-8.0676600730643268e-07</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>-5.9027145355914464e-07</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>2.0062685353009225e-06</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>6.2867796367939305e-05</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>-2.8720275011006757e-06</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>1.4648287515419824e-06</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>-1.5756447824347835e-05</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>-1.2175861309521671e-05</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>-1.6420196828498262e-05</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>-1.3139516654432279e-05</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>-1.6782417198179557e-05</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>-1.4553139778668304e-05</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.0009972833605030177</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>8.2637339942828717e-05</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>-6.718138104762163e-05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.028029412967121553</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>5.9263874135765773e-07</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>-1.2858890292298362e-08</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>2.4868477724590087e-05</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>1.9608496765550634e-05</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>-3.7787045133968205e-07</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>-1.2015106032298894e-08</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>7.1848047657407536e-06</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>7.2870750219949015e-05</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>4.652882090423984e-05</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>3.5637795246085398e-05</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>1.6609350624722869e-05</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>1.9082985864348929e-05</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>-2.5394861157167082e-05</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>-2.4293263148533335e-05</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>-1.6813507572433465e-05</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>-2.5737423556484971e-05</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>8.2637339942828717e-05</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.0013075935063921456</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>-9.4371289690258322e-05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20">
+        <v>43</v>
+      </c>
+      <c r="B20" s="1">
         <v>-1.8188041096312977</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-0.00056777032753146776</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>5.0894016828351108e-06</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>-0.0047529200038380773</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>-0.0049375891050917166</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>9.8010531083634879e-05</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>9.9549391511388215e-05</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>0.00056370649673035767</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>-0.0022434155287022039</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>-0.0067783910479097325</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>-0.0067882404363312282</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>-0.0068995549192295558</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>-0.0075117281763161419</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-0.0004289266914254419</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>-0.00040441706406298079</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>-0.00037532611098678253</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>-0.00041468101002394367</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>-6.718138104762163e-05</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>-9.4371289690258322e-05</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.021440299967321195</v>
       </c>
     </row>
